--- a/Lease_Comparables_Adams_County_Packages.xlsx
+++ b/Lease_Comparables_Adams_County_Packages.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Notes &amp; Data Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lease Comparables'!$A$4:$W$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lease Comparables'!$A$4:$W$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -121,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -248,6 +247,66 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -819,7 +878,7 @@
           <t>SW DIA/Pena Blvd</t>
         </is>
       </c>
-      <c r="I5" s="34" t="n">
+      <c r="I5" s="66" t="n">
         <v>85253</v>
       </c>
       <c r="J5" s="25" t="n">
@@ -836,7 +895,7 @@
           <t>1 Year</t>
         </is>
       </c>
-      <c r="N5" s="35" t="n">
+      <c r="N5" s="67" t="n">
         <v>6.34</v>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -916,7 +975,7 @@
           <t>East I-70/270</t>
         </is>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I6" s="66" t="n">
         <v>96460</v>
       </c>
       <c r="J6" s="25" t="n">
@@ -933,7 +992,7 @@
           <t>5 Years 1 Month</t>
         </is>
       </c>
-      <c r="N6" s="35" t="n">
+      <c r="N6" s="67" t="n">
         <v>7.35</v>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -1013,7 +1072,7 @@
           <t>SW DIA/Pena Blvd</t>
         </is>
       </c>
-      <c r="I7" s="34" t="n">
+      <c r="I7" s="66" t="n">
         <v>43855</v>
       </c>
       <c r="J7" s="25" t="n">
@@ -1026,7 +1085,7 @@
       </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="35" t="n">
+      <c r="N7" s="67" t="n">
         <v>9.75</v>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1106,7 +1165,7 @@
           <t>SW DIA/Pena Blvd</t>
         </is>
       </c>
-      <c r="I8" s="34" t="n">
+      <c r="I8" s="66" t="n">
         <v>59916</v>
       </c>
       <c r="J8" s="25" t="n">
@@ -1123,7 +1182,7 @@
           <t>2 Years</t>
         </is>
       </c>
-      <c r="N8" s="35" t="n">
+      <c r="N8" s="67" t="n">
         <v>6.5</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -1203,7 +1262,7 @@
           <t>SW DIA/Pena Blvd</t>
         </is>
       </c>
-      <c r="I9" s="34" t="n">
+      <c r="I9" s="66" t="n">
         <v>55375</v>
       </c>
       <c r="J9" s="25" t="n">
@@ -1216,7 +1275,7 @@
       </c>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="35" t="n">
+      <c r="N9" s="67" t="n">
         <v>6.75</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1254,12 +1313,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="54" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -1272,71 +1331,71 @@
           <t>5005 Washington St</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="55" t="n">
         <v>38845</v>
       </c>
-      <c r="J10" s="28" t="n">
+      <c r="J10" s="56" t="n">
         <v>45420</v>
       </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="29" t="n">
+      <c r="K10" s="54" t="n"/>
+      <c r="L10" s="54" t="n"/>
+      <c r="M10" s="54" t="n"/>
+      <c r="N10" s="57" t="n">
         <v>11.5</v>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O10" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="P10" s="54" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="inlineStr">
+      <c r="Q10" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R10" s="11" t="inlineStr">
+      <c r="R10" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S10" s="30" t="n"/>
+      <c r="S10" s="58" t="n"/>
       <c r="T10" s="12" t="n"/>
       <c r="U10" s="12" t="n"/>
-      <c r="V10" s="17" t="n"/>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="V10" s="59" t="n"/>
+      <c r="W10" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="54" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1349,71 +1408,71 @@
           <t>5635 Franklin St</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="G11" s="54" t="n"/>
+      <c r="H11" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="55" t="n">
         <v>7500</v>
       </c>
-      <c r="J11" s="28" t="n">
+      <c r="J11" s="56" t="n">
         <v>45410</v>
       </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="29" t="n">
+      <c r="K11" s="54" t="n"/>
+      <c r="L11" s="54" t="n"/>
+      <c r="M11" s="54" t="n"/>
+      <c r="N11" s="57" t="n">
         <v>13.5</v>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P11" s="54" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
+      <c r="R11" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S11" s="30" t="n"/>
+      <c r="S11" s="58" t="n"/>
       <c r="T11" s="12" t="n"/>
       <c r="U11" s="12" t="n"/>
-      <c r="V11" s="17" t="n"/>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="V11" s="59" t="n"/>
+      <c r="W11" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="54" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -1426,71 +1485,71 @@
           <t>4930 Fox St</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="55" t="n">
         <v>8400</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="56" t="n">
         <v>45390</v>
       </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="29" t="n">
+      <c r="K12" s="54" t="n"/>
+      <c r="L12" s="54" t="n"/>
+      <c r="M12" s="54" t="n"/>
+      <c r="N12" s="57" t="n">
         <v>10.95</v>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P12" s="54" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="Q12" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R12" s="11" t="inlineStr">
+      <c r="R12" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S12" s="30" t="n"/>
+      <c r="S12" s="58" t="n"/>
       <c r="T12" s="12" t="n"/>
       <c r="U12" s="12" t="n"/>
-      <c r="V12" s="17" t="n"/>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="V12" s="59" t="n"/>
+      <c r="W12" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="54" t="n">
         <v>4</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1503,71 +1562,71 @@
           <t>5050 Fox St</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="G13" s="54" t="n"/>
+      <c r="H13" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="55" t="n">
         <v>11200</v>
       </c>
-      <c r="J13" s="28" t="n">
+      <c r="J13" s="56" t="n">
         <v>45337</v>
       </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="29" t="n">
+      <c r="K13" s="54" t="n"/>
+      <c r="L13" s="54" t="n"/>
+      <c r="M13" s="54" t="n"/>
+      <c r="N13" s="57" t="n">
         <v>11.95</v>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O13" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P13" s="54" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="inlineStr">
+      <c r="Q13" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R13" s="11" t="inlineStr">
+      <c r="R13" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S13" s="30" t="n"/>
+      <c r="S13" s="58" t="n"/>
       <c r="T13" s="12" t="n"/>
       <c r="U13" s="12" t="n"/>
-      <c r="V13" s="17" t="n"/>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="V13" s="59" t="n"/>
+      <c r="W13" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>4b</t>
         </is>
@@ -1582,71 +1641,71 @@
           <t>5050 Fox St</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="55" t="n">
         <v>3630</v>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="56" t="n">
         <v>45337</v>
       </c>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="29" t="n">
+      <c r="K14" s="54" t="n"/>
+      <c r="L14" s="54" t="n"/>
+      <c r="M14" s="54" t="n"/>
+      <c r="N14" s="57" t="n">
         <v>12.5</v>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O14" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P14" s="54" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="Q14" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R14" s="11" t="inlineStr">
+      <c r="R14" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S14" s="30" t="n"/>
+      <c r="S14" s="58" t="n"/>
       <c r="T14" s="12" t="n"/>
       <c r="U14" s="12" t="n"/>
-      <c r="V14" s="17" t="n"/>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="V14" s="59" t="n"/>
+      <c r="W14" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="54" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -1659,71 +1718,71 @@
           <t>5865-5869 Broadway</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="G15" s="54" t="n"/>
+      <c r="H15" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="55" t="n">
         <v>9138</v>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="56" t="n">
         <v>45294</v>
       </c>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="29" t="n">
+      <c r="K15" s="54" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="n"/>
+      <c r="N15" s="57" t="n">
         <v>11.25</v>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="54" t="inlineStr">
         <is>
           <t>(not stated)</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R15" s="11" t="inlineStr">
+      <c r="R15" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S15" s="30" t="n"/>
+      <c r="S15" s="58" t="n"/>
       <c r="T15" s="12" t="n"/>
       <c r="U15" s="12" t="n"/>
-      <c r="V15" s="17" t="n"/>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="V15" s="59" t="n"/>
+      <c r="W15" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="54" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>5b</t>
         </is>
@@ -1738,71 +1797,71 @@
           <t>5865-5869 Broadway</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="54" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="G16" s="54" t="n"/>
+      <c r="H16" s="54" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="55" t="n">
         <v>18233</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="56" t="n">
         <v>45261</v>
       </c>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
-      <c r="N16" s="29" t="n">
+      <c r="K16" s="54" t="n"/>
+      <c r="L16" s="54" t="n"/>
+      <c r="M16" s="54" t="n"/>
+      <c r="N16" s="57" t="n">
         <v>7.95</v>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O16" s="54" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P16" s="54" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="Q16" s="54" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R16" s="11" t="inlineStr">
+      <c r="R16" s="54" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S16" s="30" t="n"/>
+      <c r="S16" s="58" t="n"/>
       <c r="T16" s="12" t="n"/>
       <c r="U16" s="12" t="n"/>
-      <c r="V16" s="17" t="n"/>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="V16" s="59" t="n"/>
+      <c r="W16" s="54" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>R0121833 - Anchor Business Park</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="60" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="19" t="inlineStr">
@@ -1815,63 +1874,63 @@
           <t>5360 N Washington St</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="60" t="inlineStr">
         <is>
           <t>80216</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="60" t="inlineStr">
         <is>
           <t>Adams / Denver north</t>
         </is>
       </c>
-      <c r="I17" s="20" t="n">
+      <c r="I17" s="61" t="n">
         <v>7285</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="62" t="n">
         <v>45239</v>
       </c>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="inlineStr">
+      <c r="K17" s="60" t="n"/>
+      <c r="L17" s="60" t="n"/>
+      <c r="M17" s="60" t="inlineStr">
         <is>
           <t>120.0 months</t>
         </is>
       </c>
-      <c r="N17" s="32" t="n">
+      <c r="N17" s="63" t="n">
         <v>10.75</v>
       </c>
-      <c r="O17" s="18" t="inlineStr">
+      <c r="O17" s="60" t="inlineStr">
         <is>
           <t>Asking</t>
         </is>
       </c>
-      <c r="P17" s="18" t="inlineStr">
+      <c r="P17" s="60" t="inlineStr">
         <is>
           <t>(not stated)</t>
         </is>
       </c>
-      <c r="Q17" s="18" t="inlineStr">
+      <c r="Q17" s="60" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R17" s="18" t="inlineStr">
+      <c r="R17" s="60" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S17" s="33" t="n"/>
+      <c r="S17" s="64" t="n"/>
       <c r="T17" s="19" t="inlineStr">
         <is>
           <t>Integrative Environmental Systems, LLC (per lease)</t>
@@ -1882,10 +1941,10 @@
           <t>Anchor Business Park, L.L.C.</t>
         </is>
       </c>
-      <c r="V17" s="24" t="n">
+      <c r="V17" s="65" t="n">
         <v>2001</v>
       </c>
-      <c r="W17" s="18" t="inlineStr">
+      <c r="W17" s="60" t="inlineStr">
         <is>
           <t>R0121833 p.11-12</t>
         </is>
@@ -1926,7 +1985,7 @@
           <t>Adams County</t>
         </is>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="66" t="n">
         <v>51774</v>
       </c>
       <c r="J18" s="4" t="n"/>
@@ -1941,7 +2000,7 @@
           <t>10.2 years</t>
         </is>
       </c>
-      <c r="N18" s="35" t="n">
+      <c r="N18" s="67" t="n">
         <v>6.97</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -2009,7 +2068,7 @@
           <t>Adams County</t>
         </is>
       </c>
-      <c r="I19" s="34" t="n">
+      <c r="I19" s="66" t="n">
         <v>200002</v>
       </c>
       <c r="J19" s="4" t="n"/>
@@ -2024,7 +2083,7 @@
           <t>3.0 years</t>
         </is>
       </c>
-      <c r="N19" s="35" t="n">
+      <c r="N19" s="67" t="n">
         <v>5.17</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2092,7 +2151,7 @@
           <t>Adams County</t>
         </is>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I20" s="66" t="n">
         <v>210195</v>
       </c>
       <c r="J20" s="4" t="n"/>
@@ -2107,7 +2166,7 @@
           <t>10.0 years</t>
         </is>
       </c>
-      <c r="N20" s="35" t="n">
+      <c r="N20" s="67" t="n">
         <v>6.25</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -2175,7 +2234,7 @@
           <t>Denver County</t>
         </is>
       </c>
-      <c r="I21" s="34" t="n">
+      <c r="I21" s="66" t="n">
         <v>115829</v>
       </c>
       <c r="J21" s="4" t="n"/>
@@ -2190,7 +2249,7 @@
           <t>5.0 years</t>
         </is>
       </c>
-      <c r="N21" s="35" t="n">
+      <c r="N21" s="67" t="n">
         <v>6.15</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2258,7 +2317,7 @@
           <t>Denver County</t>
         </is>
       </c>
-      <c r="I22" s="34" t="n">
+      <c r="I22" s="66" t="n">
         <v>247654</v>
       </c>
       <c r="J22" s="4" t="n"/>
@@ -2273,7 +2332,7 @@
           <t>6.0 years</t>
         </is>
       </c>
-      <c r="N22" s="35" t="n">
+      <c r="N22" s="67" t="n">
         <v>6.65</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -2341,7 +2400,7 @@
           <t>Denver County</t>
         </is>
       </c>
-      <c r="I23" s="34" t="n">
+      <c r="I23" s="66" t="n">
         <v>80623</v>
       </c>
       <c r="J23" s="4" t="n"/>
@@ -2356,7 +2415,7 @@
           <t>5.0 years</t>
         </is>
       </c>
-      <c r="N23" s="35" t="n">
+      <c r="N23" s="67" t="n">
         <v>6.35</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2424,7 +2483,7 @@
           <t>Denver County</t>
         </is>
       </c>
-      <c r="I24" s="34" t="n">
+      <c r="I24" s="66" t="n">
         <v>81731</v>
       </c>
       <c r="J24" s="4" t="n"/>
@@ -2439,7 +2498,7 @@
           <t>7.3 years</t>
         </is>
       </c>
-      <c r="N24" s="35" t="n">
+      <c r="N24" s="67" t="n">
         <v>6.25</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2473,12 +2532,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="48" t="inlineStr">
         <is>
           <t>R0103518 - 5977-5995 N Broadway</t>
         </is>
       </c>
-      <c r="B25" s="39" t="n">
+      <c r="B25" s="48" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
@@ -2491,89 +2550,89 @@
           <t>500 W 53rd Pl</t>
         </is>
       </c>
-      <c r="E25" s="39" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F25" s="39" t="inlineStr">
+      <c r="F25" s="48" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="48" t="inlineStr">
         <is>
           <t>80216</t>
         </is>
       </c>
-      <c r="H25" s="39" t="inlineStr">
+      <c r="H25" s="48" t="inlineStr">
         <is>
           <t>Northwest Denver</t>
         </is>
       </c>
-      <c r="I25" s="41" t="n">
+      <c r="I25" s="49" t="n">
         <v>25208</v>
       </c>
-      <c r="J25" s="42" t="n">
+      <c r="J25" s="50" t="n">
         <v>45323</v>
       </c>
-      <c r="K25" s="42" t="n">
+      <c r="K25" s="50" t="n">
         <v>45352</v>
       </c>
-      <c r="L25" s="42" t="n">
+      <c r="L25" s="50" t="n">
         <v>46569</v>
       </c>
-      <c r="M25" s="39" t="inlineStr">
+      <c r="M25" s="48" t="inlineStr">
         <is>
           <t>3 Years</t>
         </is>
       </c>
-      <c r="N25" s="43" t="n">
+      <c r="N25" s="51" t="n">
         <v>7.95</v>
       </c>
-      <c r="O25" s="39" t="inlineStr">
+      <c r="O25" s="48" t="inlineStr">
         <is>
           <t>Effective (asking = starting = effective)</t>
         </is>
       </c>
-      <c r="P25" s="39" t="inlineStr">
+      <c r="P25" s="48" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q25" s="39" t="inlineStr">
+      <c r="Q25" s="48" t="inlineStr">
         <is>
           <t>Sublease</t>
         </is>
       </c>
-      <c r="R25" s="39" t="inlineStr">
+      <c r="R25" s="48" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S25" s="44" t="n"/>
+      <c r="S25" s="52" t="n"/>
       <c r="T25" s="40" t="n"/>
       <c r="U25" s="40" t="inlineStr">
         <is>
           <t>Streech Properties</t>
         </is>
       </c>
-      <c r="V25" s="45" t="n">
+      <c r="V25" s="53" t="n">
         <v>1971</v>
       </c>
-      <c r="W25" s="39" t="inlineStr">
+      <c r="W25" s="48" t="inlineStr">
         <is>
           <t>R0103518 p.17</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>R0103518 - 5977-5995 N Broadway</t>
         </is>
       </c>
-      <c r="B26" s="39" t="n">
+      <c r="B26" s="48" t="n">
         <v>2</v>
       </c>
       <c r="C26" s="40" t="inlineStr">
@@ -2586,67 +2645,67 @@
           <t>80 E 62nd Ave</t>
         </is>
       </c>
-      <c r="E26" s="39" t="inlineStr">
+      <c r="E26" s="48" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F26" s="39" t="inlineStr">
+      <c r="F26" s="48" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G26" s="39" t="inlineStr">
+      <c r="G26" s="48" t="inlineStr">
         <is>
           <t>80216</t>
         </is>
       </c>
-      <c r="H26" s="39" t="inlineStr">
+      <c r="H26" s="48" t="inlineStr">
         <is>
           <t>Northwest Denver</t>
         </is>
       </c>
-      <c r="I26" s="41" t="n">
+      <c r="I26" s="49" t="n">
         <v>25000</v>
       </c>
-      <c r="J26" s="42" t="n">
+      <c r="J26" s="50" t="n">
         <v>45078</v>
       </c>
-      <c r="K26" s="42" t="n">
+      <c r="K26" s="50" t="n">
         <v>45078</v>
       </c>
-      <c r="L26" s="42" t="n">
+      <c r="L26" s="50" t="n">
         <v>45809</v>
       </c>
-      <c r="M26" s="39" t="inlineStr">
+      <c r="M26" s="48" t="inlineStr">
         <is>
           <t>2 Years</t>
         </is>
       </c>
-      <c r="N26" s="43" t="n">
+      <c r="N26" s="51" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="O26" s="39" t="inlineStr">
+      <c r="O26" s="48" t="inlineStr">
         <is>
           <t>Starting</t>
         </is>
       </c>
-      <c r="P26" s="39" t="inlineStr">
+      <c r="P26" s="48" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q26" s="39" t="inlineStr">
+      <c r="Q26" s="48" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R26" s="39" t="inlineStr">
+      <c r="R26" s="48" t="inlineStr">
         <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="S26" s="44" t="n"/>
+      <c r="S26" s="52" t="n"/>
       <c r="T26" s="40" t="inlineStr">
         <is>
           <t>M&amp;M Cut Flora, LLC</t>
@@ -2657,22 +2716,22 @@
           <t>Ares Industrial Real Estate In...</t>
         </is>
       </c>
-      <c r="V26" s="45" t="n">
+      <c r="V26" s="53" t="n">
         <v>1960</v>
       </c>
-      <c r="W26" s="39" t="inlineStr">
+      <c r="W26" s="48" t="inlineStr">
         <is>
           <t>R0103518 p.17</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t>R0103518 - 5977-5995 N Broadway</t>
         </is>
       </c>
-      <c r="B27" s="39" t="n">
+      <c r="B27" s="48" t="n">
         <v>3</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
@@ -2685,61 +2744,61 @@
           <t>6401 Broadway</t>
         </is>
       </c>
-      <c r="E27" s="39" t="inlineStr">
+      <c r="E27" s="48" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="F27" s="39" t="inlineStr">
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="G27" s="39" t="inlineStr">
+      <c r="G27" s="48" t="inlineStr">
         <is>
           <t>80221</t>
         </is>
       </c>
-      <c r="H27" s="39" t="inlineStr">
+      <c r="H27" s="48" t="inlineStr">
         <is>
           <t>Northwest Denver</t>
         </is>
       </c>
-      <c r="I27" s="41" t="n">
+      <c r="I27" s="49" t="n">
         <v>1017</v>
       </c>
-      <c r="J27" s="42" t="n">
+      <c r="J27" s="50" t="n">
         <v>44743</v>
       </c>
-      <c r="K27" s="42" t="n">
+      <c r="K27" s="50" t="n">
         <v>44805</v>
       </c>
-      <c r="L27" s="42" t="n"/>
-      <c r="M27" s="39" t="n"/>
-      <c r="N27" s="43" t="n">
+      <c r="L27" s="50" t="n"/>
+      <c r="M27" s="48" t="n"/>
+      <c r="N27" s="51" t="n">
         <v>9.5</v>
       </c>
-      <c r="O27" s="39" t="inlineStr">
+      <c r="O27" s="48" t="inlineStr">
         <is>
           <t>Starting</t>
         </is>
       </c>
-      <c r="P27" s="39" t="inlineStr">
+      <c r="P27" s="48" t="inlineStr">
         <is>
           <t>NNN</t>
         </is>
       </c>
-      <c r="Q27" s="39" t="inlineStr">
+      <c r="Q27" s="48" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="R27" s="39" t="inlineStr">
+      <c r="R27" s="48" t="inlineStr">
         <is>
           <t>New Lease</t>
         </is>
       </c>
-      <c r="S27" s="44" t="n"/>
+      <c r="S27" s="52" t="n"/>
       <c r="T27" s="40" t="inlineStr">
         <is>
           <t>i9 Sports</t>
@@ -2750,24 +2809,1241 @@
           <t>Sixty-Four O One Broadway, LLC</t>
         </is>
       </c>
-      <c r="V27" s="45" t="n">
+      <c r="V27" s="53" t="n">
         <v>1984</v>
       </c>
-      <c r="W27" s="39" t="inlineStr">
+      <c r="W27" s="48" t="inlineStr">
         <is>
           <t>R0103518 p.17</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>R0187789 - 5710 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B28" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>6863-6865 E 48th Ave</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>6863-6865 E 48th Ave</t>
+        </is>
+      </c>
+      <c r="E28" s="48" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F28" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G28" s="48" t="n"/>
+      <c r="H28" s="48" t="inlineStr">
+        <is>
+          <t>Adams / Denver north</t>
+        </is>
+      </c>
+      <c r="I28" s="49" t="n">
+        <v>7300</v>
+      </c>
+      <c r="J28" s="50" t="n"/>
+      <c r="K28" s="50" t="n">
+        <v>44927</v>
+      </c>
+      <c r="L28" s="50" t="n"/>
+      <c r="M28" s="48" t="n"/>
+      <c r="N28" s="51" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="O28" s="48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P28" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q28" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R28" s="48" t="n"/>
+      <c r="S28" s="52" t="n"/>
+      <c r="T28" s="40" t="inlineStr">
+        <is>
+          <t>Raul's Boat &amp; RV Upholstery</t>
+        </is>
+      </c>
+      <c r="U28" s="40" t="n"/>
+      <c r="V28" s="53" t="n"/>
+      <c r="W28" s="40" t="inlineStr">
+        <is>
+          <t>R0187789 p.2</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>R0187789 - 5710 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B29" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>6900 E 47th Avenue Dr</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>6900 E 47th Avenue Dr</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F29" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G29" s="48" t="n"/>
+      <c r="H29" s="48" t="inlineStr">
+        <is>
+          <t>Adams / Denver north</t>
+        </is>
+      </c>
+      <c r="I29" s="49" t="n">
+        <v>6830</v>
+      </c>
+      <c r="J29" s="50" t="n"/>
+      <c r="K29" s="50" t="n">
+        <v>45261</v>
+      </c>
+      <c r="L29" s="50" t="n"/>
+      <c r="M29" s="48" t="n"/>
+      <c r="N29" s="51" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="O29" s="48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P29" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q29" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R29" s="48" t="n"/>
+      <c r="S29" s="52" t="n"/>
+      <c r="T29" s="40" t="inlineStr">
+        <is>
+          <t>Prime Controls LP</t>
+        </is>
+      </c>
+      <c r="U29" s="40" t="n"/>
+      <c r="V29" s="53" t="n"/>
+      <c r="W29" s="40" t="inlineStr">
+        <is>
+          <t>R0187789 p.2 (Flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>R0187789 - 5710 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B30" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>6660-6722 E 47th Avenue Dr</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>6660-6722 E 47th Avenue Dr</t>
+        </is>
+      </c>
+      <c r="E30" s="48" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F30" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G30" s="48" t="n"/>
+      <c r="H30" s="48" t="inlineStr">
+        <is>
+          <t>Adams / Denver north</t>
+        </is>
+      </c>
+      <c r="I30" s="49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J30" s="50" t="n"/>
+      <c r="K30" s="50" t="n">
+        <v>45139</v>
+      </c>
+      <c r="L30" s="50" t="n"/>
+      <c r="M30" s="48" t="n"/>
+      <c r="N30" s="51" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O30" s="48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P30" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q30" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R30" s="48" t="n"/>
+      <c r="S30" s="52" t="n"/>
+      <c r="T30" s="40" t="inlineStr">
+        <is>
+          <t>Midwest Connect, LLC</t>
+        </is>
+      </c>
+      <c r="U30" s="40" t="n"/>
+      <c r="V30" s="53" t="n"/>
+      <c r="W30" s="40" t="inlineStr">
+        <is>
+          <t>R0187789 p.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>R0187789 - 5710 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B31" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>6804 E 48th Ave</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>6804 E 48th Ave</t>
+        </is>
+      </c>
+      <c r="E31" s="48" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F31" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G31" s="48" t="n"/>
+      <c r="H31" s="48" t="inlineStr">
+        <is>
+          <t>Adams / Denver north</t>
+        </is>
+      </c>
+      <c r="I31" s="49" t="n">
+        <v>5808</v>
+      </c>
+      <c r="J31" s="50" t="n"/>
+      <c r="K31" s="50" t="n">
+        <v>45078</v>
+      </c>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="48" t="n"/>
+      <c r="N31" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" s="48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P31" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q31" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R31" s="48" t="n"/>
+      <c r="S31" s="52" t="n"/>
+      <c r="T31" s="40" t="inlineStr">
+        <is>
+          <t>Logistics Union, Inc</t>
+        </is>
+      </c>
+      <c r="U31" s="40" t="n"/>
+      <c r="V31" s="53" t="n"/>
+      <c r="W31" s="40" t="inlineStr">
+        <is>
+          <t>R0187789 p.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>R0187789 - 5710 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B32" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>6751-6785 E 50th Ave</t>
+        </is>
+      </c>
+      <c r="D32" s="40" t="inlineStr">
+        <is>
+          <t>6751-6785 E 50th Ave</t>
+        </is>
+      </c>
+      <c r="E32" s="48" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="F32" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G32" s="48" t="n"/>
+      <c r="H32" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I32" s="49" t="n">
+        <v>13200</v>
+      </c>
+      <c r="J32" s="50" t="n"/>
+      <c r="K32" s="50" t="n">
+        <v>45323</v>
+      </c>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="48" t="n"/>
+      <c r="N32" s="51" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="O32" s="48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P32" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q32" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R32" s="48" t="n"/>
+      <c r="S32" s="52" t="n"/>
+      <c r="T32" s="40" t="inlineStr">
+        <is>
+          <t>Aqua Rocks Colorado</t>
+        </is>
+      </c>
+      <c r="U32" s="40" t="n"/>
+      <c r="V32" s="53" t="n"/>
+      <c r="W32" s="40" t="inlineStr">
+        <is>
+          <t>R0187789 p.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>R0187789 - 5710 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B33" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>3975 E 56th Ave</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr">
+        <is>
+          <t>3975 E 56th Ave</t>
+        </is>
+      </c>
+      <c r="E33" s="48" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="F33" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G33" s="48" t="n"/>
+      <c r="H33" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I33" s="49" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J33" s="50" t="n"/>
+      <c r="K33" s="50" t="n">
+        <v>45078</v>
+      </c>
+      <c r="L33" s="50" t="n"/>
+      <c r="M33" s="48" t="n"/>
+      <c r="N33" s="51" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="O33" s="48" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P33" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q33" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R33" s="48" t="n"/>
+      <c r="S33" s="52" t="n"/>
+      <c r="T33" s="40" t="inlineStr">
+        <is>
+          <t>Sunshine Home Services</t>
+        </is>
+      </c>
+      <c r="U33" s="40" t="n"/>
+      <c r="V33" s="53" t="n"/>
+      <c r="W33" s="40" t="inlineStr">
+        <is>
+          <t>R0187789 p.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="54" t="inlineStr">
+        <is>
+          <t>R0188699 - Confluent Center 70</t>
+        </is>
+      </c>
+      <c r="B34" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Building 8</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>4555-4685 Geneva St &amp; E 47th Ave</t>
+        </is>
+      </c>
+      <c r="E34" s="54" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F34" s="54" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G34" s="54" t="inlineStr">
+        <is>
+          <t>80238</t>
+        </is>
+      </c>
+      <c r="H34" s="54" t="n"/>
+      <c r="I34" s="55" t="n">
+        <v>96460</v>
+      </c>
+      <c r="J34" s="56" t="n">
+        <v>45139</v>
+      </c>
+      <c r="K34" s="56" t="n"/>
+      <c r="L34" s="56" t="n"/>
+      <c r="M34" s="54" t="inlineStr">
+        <is>
+          <t>5.1 years</t>
+        </is>
+      </c>
+      <c r="N34" s="57" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="O34" s="54" t="inlineStr">
+        <is>
+          <t>Starting</t>
+        </is>
+      </c>
+      <c r="P34" s="54" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q34" s="54" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R34" s="54" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S34" s="58" t="n"/>
+      <c r="T34" s="12" t="n"/>
+      <c r="U34" s="12" t="n"/>
+      <c r="V34" s="59" t="n"/>
+      <c r="W34" s="12" t="inlineStr">
+        <is>
+          <t>R0188699 p.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="54" t="inlineStr">
+        <is>
+          <t>R0188699 - Confluent Center 70</t>
+        </is>
+      </c>
+      <c r="B35" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Ascent Commerce Center - Building 3</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>18146 E 84th Ave</t>
+        </is>
+      </c>
+      <c r="E35" s="54" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="F35" s="54" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G35" s="54" t="n"/>
+      <c r="H35" s="54" t="n"/>
+      <c r="I35" s="55" t="n">
+        <v>26463</v>
+      </c>
+      <c r="J35" s="56" t="n">
+        <v>45139</v>
+      </c>
+      <c r="K35" s="56" t="n"/>
+      <c r="L35" s="56" t="n"/>
+      <c r="M35" s="54" t="inlineStr">
+        <is>
+          <t>5.0 years</t>
+        </is>
+      </c>
+      <c r="N35" s="57" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O35" s="54" t="inlineStr">
+        <is>
+          <t>Starting</t>
+        </is>
+      </c>
+      <c r="P35" s="54" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q35" s="54" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R35" s="54" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S35" s="58" t="n"/>
+      <c r="T35" s="12" t="n"/>
+      <c r="U35" s="12" t="n"/>
+      <c r="V35" s="59" t="n"/>
+      <c r="W35" s="12" t="inlineStr">
+        <is>
+          <t>R0188699 p.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="54" t="inlineStr">
+        <is>
+          <t>R0188699 - Confluent Center 70</t>
+        </is>
+      </c>
+      <c r="B36" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Bldg 24</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>3500 N Windsor Dr</t>
+        </is>
+      </c>
+      <c r="E36" s="54" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F36" s="54" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G36" s="54" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="H36" s="54" t="inlineStr">
+        <is>
+          <t>SW DIA/Pena Blvd</t>
+        </is>
+      </c>
+      <c r="I36" s="55" t="n">
+        <v>59916</v>
+      </c>
+      <c r="J36" s="56" t="n">
+        <v>44866</v>
+      </c>
+      <c r="K36" s="56" t="n"/>
+      <c r="L36" s="56" t="n"/>
+      <c r="M36" s="54" t="inlineStr">
+        <is>
+          <t>2.0 years</t>
+        </is>
+      </c>
+      <c r="N36" s="57" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O36" s="54" t="inlineStr">
+        <is>
+          <t>Starting</t>
+        </is>
+      </c>
+      <c r="P36" s="54" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q36" s="54" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R36" s="54" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S36" s="58" t="n"/>
+      <c r="T36" s="12" t="n"/>
+      <c r="U36" s="12" t="n"/>
+      <c r="V36" s="59" t="n"/>
+      <c r="W36" s="12" t="inlineStr">
+        <is>
+          <t>R0188699 p.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>R0200721 - 3420 Lisbon St</t>
+        </is>
+      </c>
+      <c r="B37" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>3250 N. Himalaya Road, Suite 200</t>
+        </is>
+      </c>
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>3250 N. Himalaya Road, Suite 200</t>
+        </is>
+      </c>
+      <c r="E37" s="48" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F37" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G37" s="48" t="n"/>
+      <c r="H37" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I37" s="49" t="n">
+        <v>33056</v>
+      </c>
+      <c r="J37" s="50" t="n"/>
+      <c r="K37" s="50" t="n">
+        <v>45444</v>
+      </c>
+      <c r="L37" s="50" t="n">
+        <v>47330</v>
+      </c>
+      <c r="M37" s="48" t="inlineStr">
+        <is>
+          <t>5.2 years</t>
+        </is>
+      </c>
+      <c r="N37" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" s="48" t="inlineStr">
+        <is>
+          <t>Scheduled (effective $7.81)</t>
+        </is>
+      </c>
+      <c r="P37" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q37" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R37" s="48" t="n"/>
+      <c r="S37" s="52" t="n">
+        <v>330560</v>
+      </c>
+      <c r="T37" s="40" t="n"/>
+      <c r="U37" s="40" t="n"/>
+      <c r="V37" s="53" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W37" s="40" t="inlineStr">
+        <is>
+          <t>R0200721 p.16 - 2 months free rent; tenant TIs $22.39/SF. Free-rent loss $10,662/yr ($0.32 PSF); TI adjustment $61,667/yr ($1.87 PSF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
+        <is>
+          <t>R0200721 - 3420 Lisbon St</t>
+        </is>
+      </c>
+      <c r="B38" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>19655 East 35th Drive, Suite 700</t>
+        </is>
+      </c>
+      <c r="D38" s="40" t="inlineStr">
+        <is>
+          <t>19655 East 35th Drive, Suite 700</t>
+        </is>
+      </c>
+      <c r="E38" s="48" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F38" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G38" s="48" t="n"/>
+      <c r="H38" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I38" s="49" t="n">
+        <v>48252</v>
+      </c>
+      <c r="J38" s="50" t="n"/>
+      <c r="K38" s="50" t="n">
+        <v>44774</v>
+      </c>
+      <c r="L38" s="50" t="n">
+        <v>46477</v>
+      </c>
+      <c r="M38" s="48" t="inlineStr">
+        <is>
+          <t>4.7 years</t>
+        </is>
+      </c>
+      <c r="N38" s="51" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="O38" s="48" t="inlineStr">
+        <is>
+          <t>Scheduled (effective $7.16)</t>
+        </is>
+      </c>
+      <c r="P38" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q38" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R38" s="48" t="n"/>
+      <c r="S38" s="52" t="n">
+        <v>345506</v>
+      </c>
+      <c r="T38" s="40" t="n"/>
+      <c r="U38" s="40" t="n"/>
+      <c r="V38" s="53" t="n">
+        <v>2007</v>
+      </c>
+      <c r="W38" s="40" t="inlineStr">
+        <is>
+          <t>R0200721 p.16 - No free rent, no TI adjustment - scheduled equals effective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>R0200721 - 3420 Lisbon St</t>
+        </is>
+      </c>
+      <c r="B39" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>3559 N. Himalaya Road, Suite 100</t>
+        </is>
+      </c>
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>3559 N. Himalaya Road, Suite 100</t>
+        </is>
+      </c>
+      <c r="E39" s="48" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F39" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G39" s="48" t="n"/>
+      <c r="H39" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I39" s="49" t="n">
+        <v>51774</v>
+      </c>
+      <c r="J39" s="50" t="n"/>
+      <c r="K39" s="50" t="n">
+        <v>44896</v>
+      </c>
+      <c r="L39" s="50" t="n">
+        <v>48610</v>
+      </c>
+      <c r="M39" s="48" t="inlineStr">
+        <is>
+          <t>10.2 years</t>
+        </is>
+      </c>
+      <c r="N39" s="51" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="O39" s="48" t="inlineStr">
+        <is>
+          <t>Scheduled (effective $6.97)</t>
+        </is>
+      </c>
+      <c r="P39" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q39" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R39" s="48" t="n"/>
+      <c r="S39" s="52" t="n">
+        <v>360832</v>
+      </c>
+      <c r="T39" s="40" t="n"/>
+      <c r="U39" s="40" t="n"/>
+      <c r="V39" s="53" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W39" s="40" t="inlineStr">
+        <is>
+          <t>R0200721 p.16 - No free rent or TI adjustment. This is the Erickson Metals lease AT subject property R0191099 - see Notes tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="inlineStr">
+        <is>
+          <t>R0200721 - 3420 Lisbon St</t>
+        </is>
+      </c>
+      <c r="B40" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>17654 Spinnaker Way, Suite 100</t>
+        </is>
+      </c>
+      <c r="D40" s="40" t="inlineStr">
+        <is>
+          <t>17654 Spinnaker Way, Suite 100</t>
+        </is>
+      </c>
+      <c r="E40" s="48" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F40" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G40" s="48" t="n"/>
+      <c r="H40" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I40" s="49" t="n">
+        <v>20997</v>
+      </c>
+      <c r="J40" s="50" t="n"/>
+      <c r="K40" s="50" t="n">
+        <v>45444</v>
+      </c>
+      <c r="L40" s="50" t="n">
+        <v>47361</v>
+      </c>
+      <c r="M40" s="48" t="inlineStr">
+        <is>
+          <t>5.3 years</t>
+        </is>
+      </c>
+      <c r="N40" s="51" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="O40" s="48" t="inlineStr">
+        <is>
+          <t>Scheduled (effective $11.19)</t>
+        </is>
+      </c>
+      <c r="P40" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q40" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R40" s="48" t="n"/>
+      <c r="S40" s="52" t="n">
+        <v>248814</v>
+      </c>
+      <c r="T40" s="40" t="n"/>
+      <c r="U40" s="40" t="n"/>
+      <c r="V40" s="53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W40" s="40" t="inlineStr">
+        <is>
+          <t>R0200721 p.16 - 3 months free rent; tenant TIs $1.19/SF. Free-rent loss $11,844/yr ($0.56 PSF); TI adjustment $2,082/yr ($0.10 PSF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="inlineStr">
+        <is>
+          <t>R0200721 - 3420 Lisbon St</t>
+        </is>
+      </c>
+      <c r="B41" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>17554 Spinnaker Way, Suite 2</t>
+        </is>
+      </c>
+      <c r="D41" s="40" t="inlineStr">
+        <is>
+          <t>17554 Spinnaker Way, Suite 2</t>
+        </is>
+      </c>
+      <c r="E41" s="48" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F41" s="48" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G41" s="48" t="n"/>
+      <c r="H41" s="48" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I41" s="49" t="n">
+        <v>48808</v>
+      </c>
+      <c r="J41" s="50" t="n"/>
+      <c r="K41" s="50" t="n">
+        <v>45321</v>
+      </c>
+      <c r="L41" s="50" t="n">
+        <v>47968</v>
+      </c>
+      <c r="M41" s="48" t="inlineStr">
+        <is>
+          <t>7.3 years</t>
+        </is>
+      </c>
+      <c r="N41" s="51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O41" s="48" t="inlineStr">
+        <is>
+          <t>Scheduled (effective $8.93)</t>
+        </is>
+      </c>
+      <c r="P41" s="48" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q41" s="48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R41" s="48" t="n"/>
+      <c r="S41" s="52" t="n">
+        <v>512484</v>
+      </c>
+      <c r="T41" s="40" t="n"/>
+      <c r="U41" s="40" t="n"/>
+      <c r="V41" s="53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="W41" s="40" t="inlineStr">
+        <is>
+          <t>R0200721 p.16 - 3 months free rent; tenant TIs $14.50/SF. Free-rent loss $17,667/yr ($0.36 PSF); TI adjustment $58,988/yr ($1.21 PSF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>R0200721 - 3420 Lisbon St</t>
+        </is>
+      </c>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t>subj</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>3420 Lisbon St. - THE SUBJECT (prior base period)</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>3420 N. Lisbon Street</t>
+        </is>
+      </c>
+      <c r="E42" s="60" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F42" s="60" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="H42" s="60" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="I42" s="61" t="n">
+        <v>36212</v>
+      </c>
+      <c r="J42" s="62" t="n"/>
+      <c r="K42" s="62" t="n">
+        <v>44470</v>
+      </c>
+      <c r="L42" s="62" t="n">
+        <v>46387</v>
+      </c>
+      <c r="M42" s="60" t="inlineStr">
+        <is>
+          <t>5.3 years</t>
+        </is>
+      </c>
+      <c r="N42" s="63" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O42" s="60" t="inlineStr">
+        <is>
+          <t>Scheduled (effective $5.86)</t>
+        </is>
+      </c>
+      <c r="P42" s="60" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q42" s="60" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R42" s="60" t="n"/>
+      <c r="S42" s="64" t="n">
+        <v>264348</v>
+      </c>
+      <c r="T42" s="19" t="inlineStr">
+        <is>
+          <t>Cameron Ashley Building Products, Inc.</t>
+        </is>
+      </c>
+      <c r="U42" s="19" t="inlineStr">
+        <is>
+          <t>Majestic Lisbon Buildings, LLC</t>
+        </is>
+      </c>
+      <c r="V42" s="65" t="n">
+        <v>2019</v>
+      </c>
+      <c r="W42" s="19" t="inlineStr">
+        <is>
+          <t>R0200721 p.16 - subject's own prior-base-period lease, listed at the bottom of Sterling's survey. 3 months free rent; tenant TIs $13.14/SF. The 06/01/24 rent roll shows this same lease at $280,446.36 / $7.7446 PSF and the letter text describes it as $7.60 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Highlighted row = comp 6 in the Sansone set is the subject property's own Unit B space. CoStar lists it at $10.75/SF asking; the executed lease in the same package is $9.50/SF NNN.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:W27"/>
+  <autoFilter ref="A4:W42"/>
   <mergeCells count="2">
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A1:W1"/>
@@ -2782,7 +4058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2852,19 +4128,19 @@
           <t>R0110351 (Ryan/CoStar) - Asking Rent $/SF</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="67" t="n">
         <v>6.34</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="67" t="n">
         <v>7.27</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="67" t="n">
         <v>6.75</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="67" t="n">
         <v>9.75</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2879,19 +4155,19 @@
           <t>R0110351 (Ryan/CoStar) - Starting Rent $/SF</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="67" t="n">
         <v>6.5</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="67" t="n">
         <v>7.02</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="67" t="n">
         <v>6.93</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="67" t="n">
         <v>7.35</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2906,19 +4182,19 @@
           <t>R0110351 - Months on Market</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="66" t="n">
         <v>11</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="66" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="66" t="n">
         <v>22</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2933,19 +4209,19 @@
           <t>R0110351 - Deal Size (SF)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="66" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="66" t="n">
         <v>43855</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="66" t="n">
         <v>68171</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="66" t="n">
         <v>59916</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="66" t="n">
         <v>96460</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2960,19 +4236,19 @@
           <t>R0121833 (Sansone/CoStar) - Asking Rent $/SF</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="67" t="n">
         <v>7.95</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="67" t="n">
         <v>10.99</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="67" t="n">
         <v>11.38</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="67" t="n">
         <v>13.5</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -2987,19 +4263,19 @@
           <t>R0121833 - Deal Size (SF)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="66" t="n">
         <v>3630</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="66" t="n">
         <v>13028</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="66" t="n">
         <v>8769</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="66" t="n">
         <v>38845</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -3014,19 +4290,19 @@
           <t>R0121833 - Months on Market</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D11" s="66" t="n">
         <v>13</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="66" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="66" t="n">
         <v>65</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -3041,19 +4317,19 @@
           <t>R0111559 / R0111560 (Sterling Exhibit F) - Scheduled Rent $/SF</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="66" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="67" t="n">
         <v>5.17</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="67" t="n">
         <v>6.26</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="67" t="n">
         <v>6.25</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="67" t="n">
         <v>6.97</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3068,19 +4344,19 @@
           <t>R0103518 (Ryan/CoStar) - Rent $/SF</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="67" t="n">
         <v>7.95</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="67" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="67" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="67" t="n">
         <v>9.5</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3089,30 +4365,138 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>R0187789 (Sterling/CoStar) - Rent $/SF</t>
+        </is>
+      </c>
+      <c r="B14" s="66" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="67" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="D14" s="67" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E14" s="67" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="F14" s="67" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>No summary block in the source; computed here. Simple mean $9.82; SF-weighted $9.73.</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>R0188699 (Ryan/CoStar) - Starting Rent $/SF</t>
+        </is>
+      </c>
+      <c r="B15" s="66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="67" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D15" s="67" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E15" s="67" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="F15" s="67" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>As published. Verified: simple mean $7.7833. The source separately prints a SF-weighted figure of $7.38 - verified at $7.3826.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>R0200721 (Sterling Exhibit C) - Scheduled Rent $/SF</t>
+        </is>
+      </c>
+      <c r="B16" s="66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="67" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D16" s="67" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E16" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="67" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>As published. Simple mean verified at $9.296. SF-weighted would be $8.86.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>R0200721 (Sterling Exhibit C) - Effective Rent $/SF</t>
+        </is>
+      </c>
+      <c r="B17" s="66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="67" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D17" s="67" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="E17" s="67" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="F17" s="67" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>As published, after free rent and TI amortisation. Simple mean verified at $8.412.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Applied conclusions drawn by each preparer from these sets:</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  R0110351 (Ryan): market rent $7.00/SF NNN, 10% vacancy, 8% expenses, 6.25% cap -&gt; $7,939,000 ($92.74/SF).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  R0121833 (Sansone): $9.50/SF, 5% vacancy, 15% expenses, 7.14% loaded cap -&gt; $3,919,000 ($107.45/SF).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  R0111559/60 (Sterling): survey average $6.26 -&gt; applied $6.25/SF NNN, 10% vacancy, 5% expenses, 7.63% loaded cap.</t>
         </is>
@@ -3133,7 +4517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3471,6 +4855,125 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Scope update - 15 packages</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>batch 3</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Of the 5 newest packages, 3 carry lease comparables (R0187789, R0188699, R0200721). R0191099 relies on the same 7-lease Exhibit F survey already stored for R0111559/R0111560, and R0198179 is an executed lease, not a comp set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>SUBJECT APPEARS AS ITS OWN COMP</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>R0200721 Exhibit C</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>3420 Lisbon St. is listed at the foot of its own base-period survey as a 'Prior Base period' lease at $7.30/SF scheduled, $5.86/SF effective. Its own 06/01/24 rent roll shows $7.7446/SF and the letter text says $7.60/SF - three different figures for one lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>CROSS-PORTFOLIO SELF-COMP</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>R0200721 comp 3 / R0191099</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>'3559 N. Himalaya Road, Suite 100' in the Lisbon survey is the Erickson Metals lease at subject property R0191099, and the same lease also anchors the Exhibit F survey used for buildings 6 and 7. Sterling shows it at $360,832 / $6.97 PSF in the surveys but the R0191099 rent roll carries it at $349,474.56 / $6.75 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Petitioner applied ABOVE its own survey</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>R0200721</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Sterling's survey averages $9.30/SF scheduled and $8.41/SF effective, yet the income analysis applies $11.00/SF - higher than every comp except 17654 Spinnaker Way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Repeat comps across packages</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>R0188699 comps 1 &amp; 3</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>'Building 8' (4555-4685 Geneva St) and 'Bldg 24' (3500 N Windsor Dr) are the same two transactions already captured in the R0110351 comp set, at the same $7.35 and $6.50 starting rents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>DATA GAP - sign dates</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>R0187789</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>The 6 comps report a lease start month only; no sign date, term, deal type, landlord or building size is given.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>DATA GAP - concessions</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>R0187789, R0188699</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Free rent, TI allowance and effective rent are blank for all 9 comps in these two sets. Only the R0200721 survey quantifies concessions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Lease_Comparables_Adams_County_Packages.xlsx
+++ b/Lease_Comparables_Adams_County_Packages.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Notes &amp; Data Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lease Comparables'!$A$4:$W$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lease Comparables'!$A$4:$W$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -307,6 +308,30 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -680,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W44"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4035,15 +4060,474 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="68" t="inlineStr">
+        <is>
+          <t>R0164588 - 9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="B43" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>4744 Forest St</t>
+        </is>
+      </c>
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>4744 Forest St</t>
+        </is>
+      </c>
+      <c r="E43" s="68" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F43" s="68" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G43" s="68" t="inlineStr">
+        <is>
+          <t>80216</t>
+        </is>
+      </c>
+      <c r="H43" s="68" t="inlineStr">
+        <is>
+          <t>East I-70/270</t>
+        </is>
+      </c>
+      <c r="I43" s="69" t="n">
+        <v>71060</v>
+      </c>
+      <c r="J43" s="70" t="n">
+        <v>45610</v>
+      </c>
+      <c r="K43" s="70" t="n">
+        <v>45597</v>
+      </c>
+      <c r="L43" s="70" t="n"/>
+      <c r="M43" s="68" t="inlineStr">
+        <is>
+          <t>3 Years 2 Months</t>
+        </is>
+      </c>
+      <c r="N43" s="71" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="O43" s="68" t="inlineStr">
+        <is>
+          <t>Starting</t>
+        </is>
+      </c>
+      <c r="P43" s="68" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q43" s="68" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R43" s="68" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S43" s="72" t="n"/>
+      <c r="T43" s="40" t="inlineStr">
+        <is>
+          <t>Rugby Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="U43" s="40" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="V43" s="73" t="n"/>
+      <c r="W43" s="40" t="inlineStr">
+        <is>
+          <t>R0164588 p.4-6</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>R0164588 - 9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="B44" s="68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>Upland III</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="inlineStr">
+        <is>
+          <t>3250 Abilene St</t>
+        </is>
+      </c>
+      <c r="E44" s="68" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F44" s="68" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G44" s="68" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="H44" s="68" t="inlineStr">
+        <is>
+          <t>SW DIA/Pena Blvd</t>
+        </is>
+      </c>
+      <c r="I44" s="69" t="n">
+        <v>80819</v>
+      </c>
+      <c r="J44" s="70" t="n">
+        <v>45601</v>
+      </c>
+      <c r="K44" s="70" t="n">
+        <v>45748</v>
+      </c>
+      <c r="L44" s="70" t="n"/>
+      <c r="M44" s="68" t="n"/>
+      <c r="N44" s="71" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="O44" s="68" t="inlineStr">
+        <is>
+          <t>Asking</t>
+        </is>
+      </c>
+      <c r="P44" s="68" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q44" s="68" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R44" s="68" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S44" s="72" t="n"/>
+      <c r="T44" s="40" t="inlineStr">
+        <is>
+          <t>Flexpax</t>
+        </is>
+      </c>
+      <c r="U44" s="40" t="inlineStr">
+        <is>
+          <t>Blackstone Real Estate Income Trust</t>
+        </is>
+      </c>
+      <c r="V44" s="73" t="n"/>
+      <c r="W44" s="40" t="inlineStr">
+        <is>
+          <t>R0164588 p.4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="68" t="inlineStr">
+        <is>
+          <t>R0164588 - 9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="B45" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>Building 2</t>
+        </is>
+      </c>
+      <c r="D45" s="40" t="inlineStr">
+        <is>
+          <t>11551 E 45th Ave</t>
+        </is>
+      </c>
+      <c r="E45" s="68" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F45" s="68" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G45" s="68" t="inlineStr">
+        <is>
+          <t>80239</t>
+        </is>
+      </c>
+      <c r="H45" s="68" t="inlineStr">
+        <is>
+          <t>Cent E I-70/Montbello</t>
+        </is>
+      </c>
+      <c r="I45" s="69" t="n">
+        <v>62614</v>
+      </c>
+      <c r="J45" s="70" t="n">
+        <v>45497</v>
+      </c>
+      <c r="K45" s="70" t="n">
+        <v>45627</v>
+      </c>
+      <c r="L45" s="70" t="n"/>
+      <c r="M45" s="68" t="n"/>
+      <c r="N45" s="71" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="O45" s="68" t="inlineStr">
+        <is>
+          <t>Asking</t>
+        </is>
+      </c>
+      <c r="P45" s="68" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q45" s="68" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R45" s="68" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S45" s="72" t="n"/>
+      <c r="T45" s="40" t="inlineStr">
+        <is>
+          <t>Colorado Distribution Group</t>
+        </is>
+      </c>
+      <c r="U45" s="40" t="inlineStr">
+        <is>
+          <t>Clarion Partners</t>
+        </is>
+      </c>
+      <c r="V45" s="73" t="n"/>
+      <c r="W45" s="40" t="inlineStr">
+        <is>
+          <t>R0164588 p.4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>R0164588 - 9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="B46" s="68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>4221 Monaco St</t>
+        </is>
+      </c>
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>4221 Monaco St</t>
+        </is>
+      </c>
+      <c r="E46" s="68" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F46" s="68" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G46" s="68" t="inlineStr">
+        <is>
+          <t>80216</t>
+        </is>
+      </c>
+      <c r="H46" s="68" t="inlineStr">
+        <is>
+          <t>Quebec St</t>
+        </is>
+      </c>
+      <c r="I46" s="69" t="n">
+        <v>265361</v>
+      </c>
+      <c r="J46" s="70" t="n">
+        <v>45034</v>
+      </c>
+      <c r="K46" s="70" t="n">
+        <v>45017</v>
+      </c>
+      <c r="L46" s="70" t="n"/>
+      <c r="M46" s="68" t="n"/>
+      <c r="N46" s="71" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="O46" s="68" t="inlineStr">
+        <is>
+          <t>Asking</t>
+        </is>
+      </c>
+      <c r="P46" s="68" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q46" s="68" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R46" s="68" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S46" s="72" t="n"/>
+      <c r="T46" s="40" t="inlineStr">
+        <is>
+          <t>RFMX, Corp / Houger Express LLC</t>
+        </is>
+      </c>
+      <c r="U46" s="40" t="inlineStr">
+        <is>
+          <t>Conscience Bay Company</t>
+        </is>
+      </c>
+      <c r="V46" s="73" t="n"/>
+      <c r="W46" s="40" t="inlineStr">
+        <is>
+          <t>R0164588 p.4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="68" t="inlineStr">
+        <is>
+          <t>R0164588 - 9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="B47" s="68" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>Colorado Logistics Park - Building D</t>
+        </is>
+      </c>
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>10899 Havana St</t>
+        </is>
+      </c>
+      <c r="E47" s="68" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="F47" s="68" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="G47" s="68" t="inlineStr">
+        <is>
+          <t>80640</t>
+        </is>
+      </c>
+      <c r="H47" s="68" t="inlineStr">
+        <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="I47" s="69" t="n">
+        <v>82744</v>
+      </c>
+      <c r="J47" s="70" t="n">
+        <v>44777</v>
+      </c>
+      <c r="K47" s="70" t="n">
+        <v>44958</v>
+      </c>
+      <c r="L47" s="70" t="n"/>
+      <c r="M47" s="68" t="n"/>
+      <c r="N47" s="71" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="O47" s="68" t="inlineStr">
+        <is>
+          <t>Starting</t>
+        </is>
+      </c>
+      <c r="P47" s="68" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="Q47" s="68" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="R47" s="68" t="inlineStr">
+        <is>
+          <t>New Lease</t>
+        </is>
+      </c>
+      <c r="S47" s="72" t="n"/>
+      <c r="T47" s="40" t="inlineStr">
+        <is>
+          <t>Würth</t>
+        </is>
+      </c>
+      <c r="U47" s="40" t="inlineStr">
+        <is>
+          <t>Brennan Investment Group</t>
+        </is>
+      </c>
+      <c r="V47" s="73" t="n"/>
+      <c r="W47" s="40" t="inlineStr">
+        <is>
+          <t>R0164588 p.4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Highlighted row = comp 6 in the Sansone set is the subject property's own Unit B space. CoStar lists it at $10.75/SF asking; the executed lease in the same package is $9.50/SF NNN.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:W42"/>
+  <autoFilter ref="A4:W47"/>
   <mergeCells count="2">
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A1:W1"/>
@@ -4058,7 +4542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4084,7 +4568,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4473,30 +4956,84 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>R0164588 (Ryan/CoStar) - Asking Rent $/SF</t>
+        </is>
+      </c>
+      <c r="B18" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="75" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="D18" s="75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E18" s="75" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="F18" s="75" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>As published. SF-WEIGHTED - verified at $6.3005. A simple mean would be $6.62.</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>R0164588 (Ryan/CoStar) - Starting Rent $/SF</t>
+        </is>
+      </c>
+      <c r="B19" s="74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="75" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D19" s="75" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="E19" s="75" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F19" s="75" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>As published. SF-weighted, verified at $5.8658. The 'median' column ($5.90) is the simple mean of the two deals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>Applied conclusions drawn by each preparer from these sets:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  R0110351 (Ryan): market rent $7.00/SF NNN, 10% vacancy, 8% expenses, 6.25% cap -&gt; $7,939,000 ($92.74/SF).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  R0121833 (Sansone): $9.50/SF, 5% vacancy, 15% expenses, 7.14% loaded cap -&gt; $3,919,000 ($107.45/SF).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  R0110351 (Ryan): market rent $7.00/SF NNN, 10% vacancy, 8% expenses, 6.25% cap -&gt; $7,939,000 ($92.74/SF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  R0121833 (Sansone): $9.50/SF, 5% vacancy, 15% expenses, 7.14% loaded cap -&gt; $3,919,000 ($107.45/SF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  R0111559/60 (Sterling): survey average $6.26 -&gt; applied $6.25/SF NNN, 10% vacancy, 5% expenses, 7.63% loaded cap.</t>
         </is>
@@ -4517,7 +5054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4974,6 +5511,74 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Scope update - 20 packages</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>batch 4</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Of the 5 newest packages only R0164588 carries a new comp set (5 comps). R0187787 reuses the identical 6-comp set already stored for R0187789. R0157664, R0164287 and R0180894 contain no comparables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Identical comp set across siblings</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>R0187787 / R0187789</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>Sterling used the same six CoStar comps, in the same order and at the same rents, for both 5690 and 5710 E. 56th Avenue - adjacent KEW Realty buildings protested by the same analyst on the same day. The set is stored once, tagged to R0187789.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Richer detail available</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>R0187787 p.14-16</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>The Exhibit C write-ups add asking-vs-starting rent, term, expiry, months on market, build-out, landlord and leasing rep for each of the six comps - e.g. comp 1 (6863-6865 E 48th Ave) asks $8.95/NNN but started at $9.05/NNN on a 5-year term expiring Apr 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>DATA GAP - term and concessions</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>R0164588</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>Term is reported for 1 of the 5 comps (38 months); free rent, TI allowance and effective rent are blank for all five.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
